--- a/notebooks/sensitivity analysis/ISO-NE/sensitivity_analysis_results.xlsx
+++ b/notebooks/sensitivity analysis/ISO-NE/sensitivity_analysis_results.xlsx
@@ -34,7 +34,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,11 +49,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F9F9F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -92,12 +87,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -588,7 +577,7 @@
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="3" t="n">
-        <v>0.205</v>
+        <v>0.179557</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0.2167</v>
@@ -617,728 +606,728 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>gcn_depth_1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="2" t="n">
         <v>686112</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="3" t="n">
         <v>0.1844577735536753</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="3" t="n">
         <v>1389498.14474354</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="3" t="n">
         <v>843.8818740687212</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.8194733144469496</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v>23.821685590625</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>2.610193220340928</v>
-      </c>
-      <c r="M3" s="5" t="n">
+      <c r="K3" s="3" t="n">
+        <v>22.29939072916689</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>2.458903698391641</v>
+      </c>
+      <c r="M3" s="3" t="n">
         <v>45.8076171875</v>
       </c>
-      <c r="N3" s="4" t="b">
+      <c r="N3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>gcn_depth_2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>690272</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.1841314502493787</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1382074.04239959</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>835.7763517379568</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.8204378703151456</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>23.32051311428502</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>2.649150076749173</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>56.51611328125</v>
+      </c>
+      <c r="N4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>gcn_depth_3</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>694432</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.1951005015786284</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1446766.246377336</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>863.5411961136673</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.8120329154691066</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>24.60796632199985</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>2.753075192598497</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>56.564453125</v>
+      </c>
+      <c r="N5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>gcn_depth_7</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>711072</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.191924136030116</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1412666.111588213</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>836.4162999210408</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.8164632807298885</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>27.19442588750007</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>3.11546718013094</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>56.7578125</v>
+      </c>
+      <c r="N6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>hidden_32</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>414784</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.1962176060923971</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1472455.654914106</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>885.9268390636234</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.8086952904463562</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>24.97327983777731</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2.898340831886158</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>43.1806640625</v>
+      </c>
+      <c r="N7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>hidden_128</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1321696</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.1909980549174253</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1410459.156544034</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>838.8082388910404</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.8167500132316896</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>24.7153269317452</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>2.855904160051475</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>88.2470703125</v>
+      </c>
+      <c r="N8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>hidden_256</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>2731616</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.191504153382831</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1414260.658624518</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>849.1791091035326</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.8162561136368546</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>25.35068968461508</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>2.869948073143559</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>148.10107421875</v>
+      </c>
+      <c r="N9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>kernel_3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>698656</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.187221200865491</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1402507.653577448</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>845.7276658315297</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.8177830901603299</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>25.57861697571352</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>2.915354237455131</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>56.6142578125</v>
+      </c>
+      <c r="N10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>kernel_5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>700704</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.1923450616307453</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1456631.134377862</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>873.1900652450211</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.8107512473065229</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>25.55901664042377</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>2.90744653254502</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>56.6376953125</v>
+      </c>
+      <c r="N11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>kernel_11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>706848</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.1961861248264442</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1445044.951631927</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>866.989217205058</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.8122565499060608</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>25.50353379302244</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>2.897580276440344</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>56.7080078125</v>
+      </c>
+      <c r="N12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>dilation_1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\gcn_depth_1_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>702752</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.1848920014283644</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1390609.946021585</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>844.761221414273</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.8193288667551852</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>25.52344177849184</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>2.88309614762064</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>56.6611328125</v>
+      </c>
+      <c r="N13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>gcn_depth_2</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>dilation_2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="F14" s="2" t="n">
+        <v>702752</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.1856400918628797</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1397045.195618946</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>846.2318907046091</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.8184927848324326</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>25.61680572380941</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>2.911738982954736</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>56.6611328125</v>
+      </c>
+      <c r="N14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>dilation_5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>690272</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.1841314502493787</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>1382074.04239959</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>835.7763517379568</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0.8204378703151456</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>25.09781275164832</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>2.628226964499287</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>56.51611328125</v>
-      </c>
-      <c r="N4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\gcn_depth_2_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>gcn_depth_3</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>694432</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.1951005015786284</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>1446766.246377336</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>863.5411961136673</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0.8120329154691066</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>24.66959051799997</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>2.746065639402064</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>56.564453125</v>
-      </c>
-      <c r="N5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\gcn_depth_3_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>gcn_depth_7</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>711072</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.191924136030116</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>1412666.111588213</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>836.4162999210408</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0.8164632807298885</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>27.7080276020832</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>3.156738674900159</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>56.7578125</v>
-      </c>
-      <c r="N6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\gcn_depth_7_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>hidden_32</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+      <c r="E15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>414784</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.1962176060923971</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>1472455.654914106</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>885.9268390636234</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0.8086952904463562</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>25.16410154666656</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>2.908070570086593</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>43.1806640625</v>
-      </c>
-      <c r="N7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\hidden_32_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>hidden_128</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1321696</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.1909980549174253</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>1410459.156544034</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>838.8082388910404</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>0.8167500132316896</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>24.96238611587305</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>2.879272265044303</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>88.2470703125</v>
-      </c>
-      <c r="N8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\hidden_128_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>hidden_256</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>256</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>2731616</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.1923201317541611</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>1418690.110918446</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>847.4525885986749</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0.81568062935538</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>25.37638042127656</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>2.885100308233986</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>148.10107421875</v>
-      </c>
-      <c r="N9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\hidden_256_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>kernel_3</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>698656</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.1845954359940989</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>1398041.217958831</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>845.4234322832845</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>0.8183633793975017</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>25.71362077399986</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>2.897258397453518</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>56.6142578125</v>
-      </c>
-      <c r="N10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\kernel_3_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>kernel_5</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>700704</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0.1971844487862291</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>1474121.085719628</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>875.7007424691592</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>0.8084789139765666</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>25.69815814878033</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>2.893343297488644</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>56.6376953125</v>
-      </c>
-      <c r="N11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\kernel_5_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>kernel_11</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>706848</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.1918463918132182</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>1434620.09049369</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>869.0611254248175</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0.8136109710226029</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>25.74446314599976</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>2.885992603967733</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>56.7080078125</v>
-      </c>
-      <c r="N12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\kernel_11_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>dilation_1</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="n">
+      <c r="F15" s="2" t="n">
         <v>702752</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>0.1853864060482369</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>1400003.111479722</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>849.1825963956395</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0.8181084858331784</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>26.55607490851071</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>2.910433281861267</v>
-      </c>
-      <c r="M13" s="5" t="n">
+      <c r="G15" s="3" t="n">
+        <v>0.184741204047722</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1393732.989155057</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>842.839637318318</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.8189231140538535</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>25.51358470543346</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>2.8890824355368</v>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>56.6611328125</v>
       </c>
-      <c r="N13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\dilation_1_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>dilation_2</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>702752</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.1920384065260987</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>1437457.45140993</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>867.5593478022471</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>0.8132423347895398</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>26.78753445820892</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>2.900751617737384</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>56.6611328125</v>
-      </c>
-      <c r="N14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\dilation_2_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>dilation_5</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>702752</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0.1963562229490381</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>1442845.943911145</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>869.9359018210802</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>0.8125422498739522</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>26.25467965319145</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>2.871572573156283</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>56.6611328125</v>
-      </c>
-      <c r="N15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity_Analysis\dilation_5_best_model.pth</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="N15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>— (did not beat baseline)</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1365,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA101"/>
+  <dimension ref="A1:AA97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1549,43 +1538,43 @@
         <v>0.3174882210090695</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5359029873964507</v>
+        <v>0.5359029874021908</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3159649543933694</v>
+        <v>0.3147067543126889</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2907321701868106</v>
+        <v>0.2701338883718972</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3145592500117015</v>
+        <v>0.3076034186115442</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3497736368138911</v>
+        <v>0.2907529336519436</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3073090646254314</v>
+        <v>0.3038204996346319</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3141912597250222</v>
+        <v>0.3809730551207011</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3180670711665976</v>
+        <v>0.3154474869524398</v>
       </c>
       <c r="W2" t="n">
-        <v>0.299317555114604</v>
+        <v>0.2939384844561663</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3110890991077566</v>
+        <v>0.3076609018766744</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2828229566396018</v>
+        <v>0.3769720833639518</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3168261411468968</v>
+        <v>0.3118252080195576</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3629424327292777</v>
+        <v>0.3270810469985008</v>
       </c>
     </row>
     <row r="3">
@@ -1629,46 +1618,46 @@
         <v>0.3011187991394284</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2897290077968693</v>
+        <v>0.2844154060518077</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2980306016450578</v>
+        <v>0.2752833607361203</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2812023812073691</v>
+        <v>0.2813809173997522</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2979744732557855</v>
+        <v>0.2831719962848445</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2812516836272476</v>
+        <v>0.2755522800201535</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3173444782870209</v>
+        <v>0.2793629953669289</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2731587083486856</v>
+        <v>0.2854996682491061</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2992781258786588</v>
+        <v>0.3044663332087004</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2814707109927823</v>
+        <v>0.2802974728382508</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3110785067930978</v>
+        <v>0.2885133314114322</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2765906823968345</v>
+        <v>0.2769066249636148</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3364211647887535</v>
+        <v>0.2742827986302471</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2834314251788084</v>
+        <v>0.2765380905802585</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.3297151085592014</v>
+        <v>0.2932250920068961</v>
       </c>
     </row>
     <row r="4">
@@ -1712,46 +1701,46 @@
         <v>0.2868540361408827</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2816560189470587</v>
+        <v>0.2781440608457408</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3788350847634402</v>
+        <v>0.3464543661891909</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2743066321665898</v>
+        <v>0.2764497482264029</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2707180763108337</v>
+        <v>0.265753169522516</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2734857972765203</v>
+        <v>0.2701315925926093</v>
       </c>
       <c r="S4" t="n">
-        <v>0.268191553962249</v>
+        <v>0.2782072849365063</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2707412452706374</v>
+        <v>0.2761575509255275</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2724043127488006</v>
+        <v>0.3235595637275184</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2793469144885759</v>
+        <v>0.2722091023610089</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3001032195503153</v>
+        <v>0.3114233857368008</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2687885945832187</v>
+        <v>0.2704704025844959</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.278849770876081</v>
+        <v>0.2766791348372843</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2763335335083799</v>
+        <v>0.2694295644336803</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.292032713954479</v>
+        <v>0.3076383567921737</v>
       </c>
     </row>
     <row r="5">
@@ -1795,46 +1784,46 @@
         <v>0.305482370876499</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2776822595903265</v>
+        <v>0.2785817418239764</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2876299144571018</v>
+        <v>0.2948983126106128</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2682573046373619</v>
+        <v>0.2689996415264289</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2843945395683609</v>
+        <v>0.256532359124952</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2674619996543081</v>
+        <v>0.2656827941305997</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2736703047617834</v>
+        <v>0.2853105858898218</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2663394815580966</v>
+        <v>0.2705172078630094</v>
       </c>
       <c r="U5" t="n">
-        <v>0.251372923018362</v>
+        <v>0.2647006517686581</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2707414081674223</v>
+        <v>0.272117789111231</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2699611358493796</v>
+        <v>0.2668900218015918</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2677279732205466</v>
+        <v>0.2688237061793339</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2839414882767825</v>
+        <v>0.2893585129734272</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2698480662127787</v>
+        <v>0.26535514616292</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2834081445951216</v>
+        <v>0.2917864960697243</v>
       </c>
     </row>
     <row r="6">
@@ -1878,46 +1867,46 @@
         <v>0.2865710851028906</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2742036667975697</v>
+        <v>0.2740143751302226</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3646376461697561</v>
+        <v>0.3495204741413632</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2655624675541377</v>
+        <v>0.2671239140505079</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2760837206126224</v>
+        <v>0.2600138527018309</v>
       </c>
       <c r="R6" t="n">
-        <v>0.266530502221955</v>
+        <v>0.2639473872451681</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2701883420881992</v>
+        <v>0.2793548675727541</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2635787524983348</v>
+        <v>0.2680058873812706</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3209100731251007</v>
+        <v>0.3026099115845465</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2672519037723233</v>
+        <v>0.2673398372832655</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2992443513664745</v>
+        <v>0.2727813875225182</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2656174460079613</v>
+        <v>0.2685073879278027</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2814597905870349</v>
+        <v>0.2692729175257251</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2640410713805271</v>
+        <v>0.265164688991552</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2806990091963018</v>
+        <v>0.2756165468890237</v>
       </c>
     </row>
     <row r="7">
@@ -1961,46 +1950,46 @@
         <v>0.2955029937876346</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2750431478277526</v>
+        <v>0.2766550139193077</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2950867685203789</v>
+        <v>0.3026482183170521</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2651567678698454</v>
+        <v>0.2633127935946542</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2653106350038424</v>
+        <v>0.2712576691985406</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2646905765252973</v>
+        <v>0.2624268409188005</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2827023408836319</v>
+        <v>0.3125500851045313</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2649853843887729</v>
+        <v>0.2664840767190845</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2905407808663665</v>
+        <v>0.301866392887704</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2667007766671725</v>
+        <v>0.2708811489057011</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2640382313357525</v>
+        <v>0.3038867808338858</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2652279143067739</v>
+        <v>0.2667191647847514</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2794318291113262</v>
+        <v>0.2600044774893207</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2641367364005178</v>
+        <v>0.2630229965775959</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2737392468983523</v>
+        <v>0.2912286233662044</v>
       </c>
     </row>
     <row r="8">
@@ -2044,46 +2033,46 @@
         <v>0.2876870233812391</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2734633359196019</v>
+        <v>0.267610633260886</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3302879540998782</v>
+        <v>0.2663447262865645</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2648635288423374</v>
+        <v>0.2648984339195958</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2812441266349909</v>
+        <v>0.2653360859087693</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2651358682754611</v>
+        <v>0.2628541795290575</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2598126251480107</v>
+        <v>0.2869624464854437</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2630298566727414</v>
+        <v>0.2637246987505331</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2770007091196963</v>
+        <v>0.277350993413702</v>
       </c>
       <c r="V8" t="n">
-        <v>0.266417494097586</v>
+        <v>0.2637431114865852</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2735351530206497</v>
+        <v>0.2721581280788261</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2623465166288651</v>
+        <v>0.2616750765283984</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2697526044248157</v>
+        <v>0.2839080296106671</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2658778579890235</v>
+        <v>0.2617003364442301</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.29974205764398</v>
+        <v>0.265837661181512</v>
       </c>
     </row>
     <row r="9">
@@ -2127,46 +2116,46 @@
         <v>0.2874632161254141</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2776861845877422</v>
+        <v>0.2650210443953406</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3059038084792475</v>
+        <v>0.2577911421989531</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2664186972547476</v>
+        <v>0.2669903205299735</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2681203727425293</v>
+        <v>0.2801097634123589</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2638444298693587</v>
+        <v>0.2589621931884037</v>
       </c>
       <c r="S9" t="n">
-        <v>0.260082957654824</v>
+        <v>0.2357564253132727</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2598316577524871</v>
+        <v>0.2609526402594075</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2683434184979309</v>
+        <v>0.2985899398111966</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2665148424792819</v>
+        <v>0.2644623353430801</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2579450611547439</v>
+        <v>0.2655960049175977</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2634930348385526</v>
+        <v>0.2652436489285516</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2691891259515231</v>
+        <v>0.2764916323636227</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2671121702036889</v>
+        <v>0.2617144556485178</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2756230283861489</v>
+        <v>0.2959453917362473</v>
       </c>
     </row>
     <row r="10">
@@ -2210,46 +2199,46 @@
         <v>0.2840886578589494</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2670856790794137</v>
+        <v>0.2636135482298564</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2633052994576046</v>
+        <v>0.2658906143290695</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2632527690119117</v>
+        <v>0.2587090315497365</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2766027814509183</v>
+        <v>0.2264712158452794</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2602287522624901</v>
+        <v>0.2532341654474023</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2606967212704049</v>
+        <v>0.2512236315418374</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2553774765384776</v>
+        <v>0.2568408483485422</v>
       </c>
       <c r="U10" t="n">
-        <v>0.238616405809743</v>
+        <v>0.2330655468734001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2640425096427606</v>
+        <v>0.2637493566471375</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2737863891039084</v>
+        <v>0.2742842168350617</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2641870735082313</v>
+        <v>0.2634611577103453</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2713008766623647</v>
+        <v>0.2651443291966372</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2619546663039172</v>
+        <v>0.261602174506084</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2819761060987627</v>
+        <v>0.2926538187281468</v>
       </c>
     </row>
     <row r="11">
@@ -2293,46 +2282,46 @@
         <v>0.3016409219195277</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2615177412594338</v>
+        <v>0.2616917113773525</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2719825040462939</v>
+        <v>0.2620097545215226</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2637334434269381</v>
+        <v>0.2543999168652394</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2641738740230791</v>
+        <v>0.2267159414613973</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2620924625291743</v>
+        <v>0.2516279465957614</v>
       </c>
       <c r="S11" t="n">
-        <v>0.274994541987065</v>
+        <v>0.233477444228686</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2514897174671415</v>
+        <v>0.2531860336076376</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2469825419627463</v>
+        <v>0.2339311681073647</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2631394558178246</v>
+        <v>0.2674628448410898</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2803060102903604</v>
+        <v>0.2726564438832789</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2632010960489635</v>
+        <v>0.2626015227326492</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2798092074330626</v>
+        <v>0.2662655893965798</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.2612152206249658</v>
+        <v>0.260856343617986</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2678367482650399</v>
+        <v>0.281856486404484</v>
       </c>
     </row>
     <row r="12">
@@ -2376,46 +2365,46 @@
         <v>0.2833501236349666</v>
       </c>
       <c r="N12" t="n">
-        <v>0.262839518352758</v>
+        <v>0.2611507801415999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2671352736594497</v>
+        <v>0.2613672236603425</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2637910868064308</v>
+        <v>0.252999491154501</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.279684386452881</v>
+        <v>0.2349347764875837</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2614701660850262</v>
+        <v>0.2487829125001411</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2731907563929795</v>
+        <v>0.2378389363812831</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2526118894076853</v>
+        <v>0.2526125948729902</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2393779752773157</v>
+        <v>0.2364223930433691</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2632185114886273</v>
+        <v>0.2664136354318889</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2744347008493355</v>
+        <v>0.2907783246049528</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2637416861935957</v>
+        <v>0.2564107353090932</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2687362895271123</v>
+        <v>0.2308991500800719</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2649274000336131</v>
+        <v>0.262027040223999</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2806163862669045</v>
+        <v>0.2790977879268087</v>
       </c>
     </row>
     <row r="13">
@@ -2459,46 +2448,46 @@
         <v>0.2600550222654004</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2613213598835936</v>
+        <v>0.2597911633697361</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2639565217281435</v>
+        <v>0.2700034860917618</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2594631942766449</v>
+        <v>0.251767415191578</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2510709959657745</v>
+        <v>0.2310724294671246</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2556799025744323</v>
+        <v>0.247247351814554</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2276342820393378</v>
+        <v>0.2393266099386021</v>
       </c>
       <c r="T13" t="n">
-        <v>0.250030324409508</v>
+        <v>0.2536332296238334</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2357980626447267</v>
+        <v>0.2342811962948375</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2616628252685624</v>
+        <v>0.2647306167074164</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2669933245033714</v>
+        <v>0.2590688707418912</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2616263887082989</v>
+        <v>0.2545114840757995</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2655757543772964</v>
+        <v>0.2511440206732377</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2605782571587373</v>
+        <v>0.2570229068991136</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2727240841313393</v>
+        <v>0.2517375242889203</v>
       </c>
     </row>
     <row r="14">
@@ -2542,46 +2531,46 @@
         <v>0.3105529239702574</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2608415252175028</v>
+        <v>0.2504594144180479</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2643864184836118</v>
+        <v>0.2209272130015084</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2624316401279355</v>
+        <v>0.2500249554002889</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2669123017066983</v>
+        <v>0.2346745597855841</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2512601017182277</v>
+        <v>0.2448900529829985</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2356381024533914</v>
+        <v>0.2329347005518633</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2484311485770813</v>
+        <v>0.2524257886362039</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2359822166851149</v>
+        <v>0.2355284243104592</v>
       </c>
       <c r="V14" t="n">
-        <v>0.257881349118134</v>
+        <v>0.2656442446841989</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2291152853495764</v>
+        <v>0.2643843679868247</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2625440427079058</v>
+        <v>0.2542804209746359</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2854168709878378</v>
+        <v>0.2407250815689655</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.2601029655880733</v>
+        <v>0.2549896571777515</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.2661335710522206</v>
+        <v>0.259629676239034</v>
       </c>
     </row>
     <row r="15">
@@ -2625,46 +2614,46 @@
         <v>0.2586331189522528</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2506103573851903</v>
+        <v>0.2450865159380781</v>
       </c>
       <c r="O15" t="n">
-        <v>0.217904469001183</v>
+        <v>0.223453880300622</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2619144438519643</v>
+        <v>0.23851788433438</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2543533065532821</v>
+        <v>0.204271609362542</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2509988038531266</v>
+        <v>0.2437372663373913</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2309049466805667</v>
+        <v>0.2305930518589696</v>
       </c>
       <c r="T15" t="n">
-        <v>0.247068773939713</v>
+        <v>0.2428854864267709</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2344304885405284</v>
+        <v>0.2087404181311145</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2543050983866815</v>
+        <v>0.2627867697006908</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2464887594548736</v>
+        <v>0.269454422988032</v>
       </c>
       <c r="X15" t="n">
-        <v>0.262029863651534</v>
+        <v>0.2530002199990813</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2864985908302715</v>
+        <v>0.2315747460841168</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.261298832268077</v>
+        <v>0.2552524379546915</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.2763271712897509</v>
+        <v>0.2477387452500948</v>
       </c>
     </row>
     <row r="16">
@@ -2708,46 +2697,46 @@
         <v>0.2914073081121698</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2456874005296383</v>
+        <v>0.2426935658628537</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2249941965148932</v>
+        <v>0.2195388809541019</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2632028198654741</v>
+        <v>0.2350305807045545</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2857345025182826</v>
+        <v>0.2080116916551199</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2493406196994599</v>
+        <v>0.2430078238017919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2223855472113851</v>
+        <v>0.2272374698510523</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2473236374318415</v>
+        <v>0.2384703737098631</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2286505043931386</v>
+        <v>0.2070888178408697</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2533689123070376</v>
+        <v>0.2630666302139909</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2366730562240482</v>
+        <v>0.2557277512436701</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2647007332175724</v>
+        <v>0.2521017198104504</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.268910566195616</v>
+        <v>0.23617576272765</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.2620665102789163</v>
+        <v>0.2536194017541802</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.2687095242863857</v>
+        <v>0.2451933674623354</v>
       </c>
     </row>
     <row r="17">
@@ -2791,46 +2780,46 @@
         <v>0.2947717728337219</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2447865785884648</v>
+        <v>0.2396619087546941</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2189342622919287</v>
+        <v>0.2164180653488324</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2612055513030303</v>
+        <v>0.2341513111802541</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2412609424017289</v>
+        <v>0.2026680381495063</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2487070629265437</v>
+        <v>0.2419767494136391</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2387676191486085</v>
+        <v>0.227282009585452</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2449770946101832</v>
+        <v>0.2384582743287271</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2369584402611884</v>
+        <v>0.2076891689534042</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2535477391451844</v>
+        <v>0.2660611906735427</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2337132281148792</v>
+        <v>0.3038047243638656</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2656002748865357</v>
+        <v>0.24210011386428</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2636804192202117</v>
+        <v>0.2055062513299091</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.2619373514393945</v>
+        <v>0.2519120326003998</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.2951568054617921</v>
+        <v>0.2384983540780969</v>
       </c>
     </row>
     <row r="18">
@@ -2874,46 +2863,46 @@
         <v>0.309562082636315</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2419400892628372</v>
+        <v>0.2377164724421464</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2139505476695134</v>
+        <v>0.2124743863813958</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2618025788029055</v>
+        <v>0.2323484555664203</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2546944724989966</v>
+        <v>0.2036525227031879</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2487268994777841</v>
+        <v>0.241865758160668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2340519119036859</v>
+        <v>0.2200741761913652</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2442878264864553</v>
+        <v>0.2364724181392346</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2270326756761741</v>
+        <v>0.2066657218640134</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2504378404383632</v>
+        <v>0.2648981289460886</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2292563959164043</v>
+        <v>0.2669762523388504</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2616511865880741</v>
+        <v>0.2378368320767114</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.2588459817213343</v>
+        <v>0.2108524612715046</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.2607222206713555</v>
+        <v>0.2503863429719936</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2809061009626267</v>
+        <v>0.2415364126894388</v>
       </c>
     </row>
     <row r="19">
@@ -2957,46 +2946,46 @@
         <v>0.2717474356999704</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2390113863901597</v>
+        <v>0.2351736287463241</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2114851668086735</v>
+        <v>0.207697729902982</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2623116169240295</v>
+        <v>0.2297960365506674</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.252839117289416</v>
+        <v>0.1980726088128858</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2474948621993838</v>
+        <v>0.2408363878388297</v>
       </c>
       <c r="S19" t="n">
-        <v>0.230164830554248</v>
+        <v>0.2210596439289431</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2446438036974489</v>
+        <v>0.2334434863618644</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2289098848047765</v>
+        <v>0.2077224264107932</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2413180662465305</v>
+        <v>0.262874741164952</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2070541901798066</v>
+        <v>0.2726571162235571</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2644444581944773</v>
+        <v>0.2365185583379766</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2647523075795642</v>
+        <v>0.2072365678192471</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.254570109508008</v>
+        <v>0.2473162380970768</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.2433902545816312</v>
+        <v>0.231865668428261</v>
       </c>
     </row>
     <row r="20">
@@ -3040,46 +3029,46 @@
         <v>0.2441260190436671</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2375162877065461</v>
+        <v>0.2341787173597465</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2127934335594644</v>
+        <v>0.207673359369552</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2650393832913669</v>
+        <v>0.2283212272681234</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2545465102106425</v>
+        <v>0.1996795036708032</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2455171322650161</v>
+        <v>0.2409460884865281</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2337881516957963</v>
+        <v>0.2202034682259308</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2427501758206482</v>
+        <v>0.2322906447374377</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2289267776875494</v>
+        <v>0.2063154951053656</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2376115516497761</v>
+        <v>0.264655787070582</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2079586982755751</v>
+        <v>0.2598174783460027</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2621238196253284</v>
+        <v>0.2341244145573602</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.2663463482888665</v>
+        <v>0.2027002013186552</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.2538811894641681</v>
+        <v>0.2462779891731079</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.2438460507176139</v>
+        <v>0.2346710503095609</v>
       </c>
     </row>
     <row r="21">
@@ -3123,46 +3112,46 @@
         <v>0.2564787727756245</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2357675774092209</v>
+        <v>0.2328136937638883</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2097871919809762</v>
+        <v>0.2049474422640536</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2603352433917197</v>
+        <v>0.2278073999784456</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2547270877714425</v>
+        <v>0.2008699737647075</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2358427755419196</v>
+        <v>0.2390536041583958</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2035186175222527</v>
+        <v>0.2173251622200058</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2407004322725818</v>
+        <v>0.23020675928863</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2342016821948149</v>
+        <v>0.1989539559236017</v>
       </c>
       <c r="V21" t="n">
-        <v>0.236948602913671</v>
+        <v>0.2603850037452172</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2068923059563929</v>
+        <v>0.2247377983330303</v>
       </c>
       <c r="X21" t="n">
-        <v>0.2642270636952613</v>
+        <v>0.2320624448105016</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.2754569943988543</v>
+        <v>0.2029172156683423</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.2540699611533402</v>
+        <v>0.245019912434942</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.2469287751205208</v>
+        <v>0.2324468026221809</v>
       </c>
     </row>
     <row r="22">
@@ -3206,46 +3195,46 @@
         <v>0.2400421727770145</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2344318938803328</v>
+        <v>0.2316490102959566</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2070288826124556</v>
+        <v>0.2035195034955885</v>
       </c>
       <c r="P22" t="n">
-        <v>0.251445168186718</v>
+        <v>0.2264100256499119</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2251873993370768</v>
+        <v>0.2003260037527407</v>
       </c>
       <c r="R22" t="n">
-        <v>0.232946100275317</v>
+        <v>0.2398392465658301</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2042778612319696</v>
+        <v>0.2163540641698292</v>
       </c>
       <c r="T22" t="n">
-        <v>0.241377627950408</v>
+        <v>0.2277302235241764</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2217721045275544</v>
+        <v>0.2008478290161752</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2357643359179093</v>
+        <v>0.2551934932558682</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2016856759551264</v>
+        <v>0.2323827511316685</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2636521591974253</v>
+        <v>0.2295739666697346</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.2506899861776728</v>
+        <v>0.2005032758603019</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.2540259599062222</v>
+        <v>0.2441164953672627</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.2457931109593581</v>
+        <v>0.2376393578309445</v>
       </c>
     </row>
     <row r="23">
@@ -3289,46 +3278,46 @@
         <v>0.2468277062956697</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2333890376804966</v>
+        <v>0.2301271695120276</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2042619790738371</v>
+        <v>0.2035633814829662</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2491981185210699</v>
+        <v>0.2262587470179501</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2300642284755531</v>
+        <v>0.1989306679845017</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2321449769930221</v>
+        <v>0.2389754272905017</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2079837502616075</v>
+        <v>0.2170999853833017</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2405557013116777</v>
+        <v>0.2271904266816525</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2251360165715814</v>
+        <v>0.1989696671962394</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2346214557543767</v>
+        <v>0.2550110732097456</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2021891417265949</v>
+        <v>0.229545518532051</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2646968644535677</v>
+        <v>0.2289143184022901</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.2779383905668196</v>
+        <v>0.2022963042854574</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.2528761242524036</v>
+        <v>0.2439769607745419</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.2467804616532405</v>
+        <v>0.2378459993106972</v>
       </c>
     </row>
     <row r="24">
@@ -3372,46 +3361,46 @@
         <v>0.2361710364822706</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2319909788683549</v>
+        <v>0.2303125546891088</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2067179763216083</v>
+        <v>0.2020205877841851</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2479755673865395</v>
+        <v>0.2205512104555964</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2267286133233498</v>
+        <v>0.1992633545940573</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2315771883961645</v>
+        <v>0.2391733287733571</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2013448178395055</v>
+        <v>0.2254504778799823</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2399062904652424</v>
+        <v>0.2261630218545329</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2203006176636748</v>
+        <v>0.198193855118724</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2327833309161577</v>
+        <v>0.2542614685217581</v>
       </c>
       <c r="W24" t="n">
-        <v>0.200732475115081</v>
+        <v>0.2231099107123349</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2601255010928928</v>
+        <v>0.2276667413101647</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.2532197935176649</v>
+        <v>0.1996325535185991</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.2432247396704764</v>
+        <v>0.2335733790874235</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.2101074403642644</v>
+        <v>0.2049294531385548</v>
       </c>
     </row>
     <row r="25">
@@ -3455,46 +3444,46 @@
         <v>0.2419707351787524</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2318500090613653</v>
+        <v>0.2297950241337569</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2045046248328291</v>
+        <v>0.2073297836345682</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2470314242099681</v>
+        <v>0.2197482792375809</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.229095042546858</v>
+        <v>0.1968257108772136</v>
       </c>
       <c r="R25" t="n">
-        <v>0.230512309881035</v>
+        <v>0.2386097329330038</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2006003093835431</v>
+        <v>0.2188111907029051</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2389094761826775</v>
+        <v>0.2255704362245569</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2188681720057144</v>
+        <v>0.1964479742732433</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2318985534154556</v>
+        <v>0.2539029586752338</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2037234452103935</v>
+        <v>0.234029329856872</v>
       </c>
       <c r="X25" t="n">
-        <v>0.2640456105505447</v>
+        <v>0.2261619906533848</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.2686290759334946</v>
+        <v>0.1974932274111017</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.240372073875109</v>
+        <v>0.230853777409585</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.208985934541984</v>
+        <v>0.2031256626596895</v>
       </c>
     </row>
     <row r="26">
@@ -3538,46 +3527,46 @@
         <v>0.2342349198461727</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2308931437105494</v>
+        <v>0.2295752272148393</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2066335587436549</v>
+        <v>0.201444054840388</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2463657035692479</v>
+        <v>0.2189616726457395</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2254734926057753</v>
+        <v>0.1972304209693692</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2300117081300594</v>
+        <v>0.2382482912714693</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2039818580596721</v>
+        <v>0.2218879480632409</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2383900502858268</v>
+        <v>0.2244455942437668</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2232198762421845</v>
+        <v>0.1978045334603253</v>
       </c>
       <c r="V26" t="n">
-        <v>0.231031595594596</v>
+        <v>0.2507546662337585</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2022039222147873</v>
+        <v>0.2328225449646015</v>
       </c>
       <c r="X26" t="n">
-        <v>0.2610024497036106</v>
+        <v>0.2256020888847814</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.2713528636997947</v>
+        <v>0.2024042565900781</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.2389780021626656</v>
+        <v>0.2299671460381778</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.2104130402000733</v>
+        <v>0.2016223037388687</v>
       </c>
     </row>
     <row r="27">
@@ -3621,46 +3610,46 @@
         <v>0.2384723752926467</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2307111397539535</v>
+        <v>0.2288657601784207</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2046510379744237</v>
+        <v>0.2011927051156851</v>
       </c>
       <c r="P27" t="n">
-        <v>0.2346970358062997</v>
+        <v>0.2191089415684158</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2057629199684217</v>
+        <v>0.1987910846302799</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2288403485378266</v>
+        <v>0.2290828786405527</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1971844487862291</v>
+        <v>0.1971137153920366</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2386287681158047</v>
+        <v>0.2234145367810549</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2219109876118658</v>
+        <v>0.1969962849788287</v>
       </c>
       <c r="V27" t="n">
-        <v>0.2297721378166567</v>
+        <v>0.2499390007112144</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1991209369497187</v>
+        <v>0.235298292697027</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2541944763530816</v>
+        <v>0.2250980879911337</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.2312747365142146</v>
+        <v>0.1982125966380621</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.2376258640188323</v>
+        <v>0.2287149370709542</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.2066767824747713</v>
+        <v>0.1975208900478569</v>
       </c>
     </row>
     <row r="28">
@@ -3704,46 +3693,46 @@
         <v>0.2423731580416805</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2246213639231999</v>
+        <v>0.2281312419886678</v>
       </c>
       <c r="O28" t="n">
-        <v>0.195280615299171</v>
+        <v>0.1984056522093931</v>
       </c>
       <c r="P28" t="n">
-        <v>0.2327025892436196</v>
+        <v>0.2183811464539367</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.206183284655994</v>
+        <v>0.1970675247900751</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2277330553028271</v>
+        <v>0.2266395074384641</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1991740899513517</v>
+        <v>0.1982823280927557</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2384423658728969</v>
+        <v>0.2237214368406283</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2140916347337201</v>
+        <v>0.2014972846151454</v>
       </c>
       <c r="V28" t="n">
-        <v>0.2282084765159025</v>
+        <v>0.2507267204798327</v>
       </c>
       <c r="W28" t="n">
-        <v>0.1992902824158661</v>
+        <v>0.2333996649573231</v>
       </c>
       <c r="X28" t="n">
-        <v>0.2529045257117014</v>
+        <v>0.2249337483143573</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.2391126467796109</v>
+        <v>0.1992982533704403</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.2339277566210482</v>
+        <v>0.2274263117939603</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.208612267964036</v>
+        <v>0.2005814527676588</v>
       </c>
     </row>
     <row r="29">
@@ -3787,46 +3776,46 @@
         <v>0.2384647050146329</v>
       </c>
       <c r="N29" t="n">
-        <v>0.222812203536472</v>
+        <v>0.2274414752648512</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1932104478786787</v>
+        <v>0.201900392742067</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2321405890012883</v>
+        <v>0.218336960831888</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2033131196520913</v>
+        <v>0.1976479627981277</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2264025319282982</v>
+        <v>0.2259505835307901</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1999381707065691</v>
+        <v>0.1969526240671016</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2367008402096954</v>
+        <v>0.223044683864294</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2198156622684746</v>
+        <v>0.1961861248264442</v>
       </c>
       <c r="V29" t="n">
-        <v>0.2279540294250242</v>
+        <v>0.2385729386640543</v>
       </c>
       <c r="W29" t="n">
-        <v>0.1972475569316391</v>
+        <v>0.2059351251459177</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2524354175764544</v>
+        <v>0.2246314487766382</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.2324497250320594</v>
+        <v>0.1981443984359388</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2329584023268693</v>
+        <v>0.2278033138891636</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.201329962834027</v>
+        <v>0.2042988715894256</v>
       </c>
     </row>
     <row r="30">
@@ -3870,46 +3859,46 @@
         <v>0.2342162866501255</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2224533277571448</v>
+        <v>0.226860896838167</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1934849086729881</v>
+        <v>0.2008579155080055</v>
       </c>
       <c r="P30" t="n">
-        <v>0.2319141024231049</v>
+        <v>0.2159652051454302</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1997792877928456</v>
+        <v>0.2018470176034973</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2261884581020548</v>
+        <v>0.2253702878490214</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1982295846735889</v>
+        <v>0.1967698924418522</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2377426847930967</v>
+        <v>0.2226576793646394</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2251660735855806</v>
+        <v>0.1988120725312384</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2272731997726932</v>
+        <v>0.2355390437686246</v>
       </c>
       <c r="W30" t="n">
-        <v>0.1975033202342035</v>
+        <v>0.2084105748264191</v>
       </c>
       <c r="X30" t="n">
-        <v>0.2510924039231536</v>
+        <v>0.2191794888839926</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.2443436793810781</v>
+        <v>0.2012602395144146</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.2311932695144402</v>
+        <v>0.2266286393158015</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.202859865010749</v>
+        <v>0.1980210399392918</v>
       </c>
     </row>
     <row r="31">
@@ -3953,46 +3942,46 @@
         <v>0.2044179189709146</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2220212482493217</v>
+        <v>0.2270847818821915</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1936067439477965</v>
+        <v>0.2019041787046589</v>
       </c>
       <c r="P31" t="n">
-        <v>0.2308384094672077</v>
+        <v>0.2158292260421209</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2003478327126046</v>
+        <v>0.2006877902809112</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2260381597024966</v>
+        <v>0.2256851522944683</v>
       </c>
       <c r="S31" t="n">
-        <v>0.2005481704228625</v>
+        <v>0.1934102540333484</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2367741222270141</v>
+        <v>0.2220053412328082</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2202015201258365</v>
+        <v>0.1994240914610644</v>
       </c>
       <c r="V31" t="n">
-        <v>0.2268490753606085</v>
+        <v>0.2354220992939408</v>
       </c>
       <c r="W31" t="n">
-        <v>0.1983035326704314</v>
+        <v>0.2092259244703457</v>
       </c>
       <c r="X31" t="n">
-        <v>0.2499998013127195</v>
+        <v>0.2176985298437336</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.2230868423084954</v>
+        <v>0.1953190003115632</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.2295723148844828</v>
+        <v>0.2255052048597516</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.1996298917986808</v>
+        <v>0.2030513994711435</v>
       </c>
     </row>
     <row r="32">
@@ -4036,46 +4025,46 @@
         <v>0.2002573857810032</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2215838063977782</v>
+        <v>0.2265271883734987</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1927435720261927</v>
+        <v>0.2009877198905281</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2298011273214948</v>
+        <v>0.2153482207882195</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.198743015252203</v>
+        <v>0.2012545660494013</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2206607290258831</v>
+        <v>0.2248865347355604</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1979013409046528</v>
+        <v>0.1965082476564176</v>
       </c>
       <c r="T32" t="n">
-        <v>0.2357072531330315</v>
+        <v>0.2224529299823459</v>
       </c>
       <c r="U32" t="n">
-        <v>0.2144818019426108</v>
+        <v>0.1985269526840519</v>
       </c>
       <c r="V32" t="n">
-        <v>0.2264690382390722</v>
+        <v>0.2340794842005207</v>
       </c>
       <c r="W32" t="n">
-        <v>0.1965654752287549</v>
+        <v>0.2079962950733667</v>
       </c>
       <c r="X32" t="n">
-        <v>0.249002100387973</v>
+        <v>0.2179908913844996</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.2409607867619886</v>
+        <v>0.1929792047439513</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.228320725847128</v>
+        <v>0.219604767281716</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.1980685873476585</v>
+        <v>0.2045748995298459</v>
       </c>
     </row>
     <row r="33">
@@ -4119,46 +4108,46 @@
         <v>0.2015319652625794</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2211066733022059</v>
+        <v>0.220041390462232</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1923201317541611</v>
+        <v>0.1959988622766889</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2292353772435122</v>
+        <v>0.2150294590733699</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2019184349256873</v>
+        <v>0.2020812886860365</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2194056734712102</v>
+        <v>0.2242361284053523</v>
       </c>
       <c r="S33" t="n">
-        <v>0.1976542957112744</v>
+        <v>0.1923450616307453</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2253874235455532</v>
+        <v>0.2216935459647543</v>
       </c>
       <c r="U33" t="n">
-        <v>0.1953208848406404</v>
+        <v>0.2057536046289034</v>
       </c>
       <c r="V33" t="n">
-        <v>0.2258605031981633</v>
+        <v>0.2335145737983533</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2013335240867064</v>
+        <v>0.2059381626638224</v>
       </c>
       <c r="X33" t="n">
-        <v>0.2502729097719897</v>
+        <v>0.2174140755818341</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.2369983065414181</v>
+        <v>0.1928792675793492</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2268666229403216</v>
+        <v>0.2182451174709915</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.1963562229490381</v>
+        <v>0.197319304726972</v>
       </c>
     </row>
     <row r="34">
@@ -4202,46 +4191,46 @@
         <v>0.2033901955151732</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2205363299682244</v>
+        <v>0.2189339830478546</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1932688225606006</v>
+        <v>0.1931928735576535</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2279883451020915</v>
+        <v>0.2142117438560798</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1996300043753464</v>
+        <v>0.1986512272892798</v>
       </c>
       <c r="R34" t="n">
-        <v>0.2194533263725683</v>
+        <v>0.2244572165760804</v>
       </c>
       <c r="S34" t="n">
-        <v>0.1983705422337323</v>
+        <v>0.1974184188765053</v>
       </c>
       <c r="T34" t="n">
-        <v>0.2236357748215972</v>
+        <v>0.2157926880869984</v>
       </c>
       <c r="U34" t="n">
-        <v>0.1994955130064937</v>
+        <v>0.2014885861670544</v>
       </c>
       <c r="V34" t="n">
-        <v>0.2252372088033922</v>
+        <v>0.2271368113184764</v>
       </c>
       <c r="W34" t="n">
-        <v>0.1963057407552523</v>
+        <v>0.1983060794904002</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2485025020716481</v>
+        <v>0.217329995056291</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.2375222025510894</v>
+        <v>0.1944038516458681</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.2257866121343653</v>
+        <v>0.2185248095803886</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.2017040822413881</v>
+        <v>0.1993921253635033</v>
       </c>
     </row>
     <row r="35">
@@ -4285,46 +4274,46 @@
         <v>0.1998877232845511</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2202444833911155</v>
+        <v>0.2193255601296863</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1955299169106412</v>
+        <v>0.1933898014032235</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2268743509280472</v>
+        <v>0.2138970101767889</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1982354636064433</v>
+        <v>0.2001538549941636</v>
       </c>
       <c r="R35" t="n">
-        <v>0.218370405006538</v>
+        <v>0.2233817665452861</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1981014490790539</v>
+        <v>0.1977320258578828</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2242930405542316</v>
+        <v>0.2151818409800714</v>
       </c>
       <c r="U35" t="n">
-        <v>0.193260905286943</v>
+        <v>0.2034176721600658</v>
       </c>
       <c r="V35" t="n">
-        <v>0.2243078691184459</v>
+        <v>0.2240779611189688</v>
       </c>
       <c r="W35" t="n">
-        <v>0.2003083468453588</v>
+        <v>0.1969647989543772</v>
       </c>
       <c r="X35" t="n">
-        <v>0.2469985776172935</v>
+        <v>0.2171352286053406</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.2383432877300241</v>
+        <v>0.1942950455954037</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.2244863076143213</v>
+        <v>0.2175735356286168</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.2006164763914924</v>
+        <v>0.1996379861369936</v>
       </c>
     </row>
     <row r="36">
@@ -4368,46 +4357,46 @@
         <v>0.1985188928879051</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2191677698904017</v>
+        <v>0.2185333282301926</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1929514431602713</v>
+        <v>0.1930483701195459</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2260972935868011</v>
+        <v>0.2136734214434323</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.1968488329662748</v>
+        <v>0.2005467434429516</v>
       </c>
       <c r="R36" t="n">
-        <v>0.2162346194636785</v>
+        <v>0.2234581590607023</v>
       </c>
       <c r="S36" t="n">
-        <v>0.1992796626019482</v>
+        <v>0.1960216509651835</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2237797198847921</v>
+        <v>0.2147391510142152</v>
       </c>
       <c r="U36" t="n">
-        <v>0.1918463918132182</v>
+        <v>0.1970015090498471</v>
       </c>
       <c r="V36" t="n">
-        <v>0.2238941595674115</v>
+        <v>0.2230252363172568</v>
       </c>
       <c r="W36" t="n">
-        <v>0.1966548495364873</v>
+        <v>0.1966066579671666</v>
       </c>
       <c r="X36" t="n">
-        <v>0.2369573893725934</v>
+        <v>0.216650352809455</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.206714314490396</v>
+        <v>0.1942750587643272</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.2239431130107153</v>
+        <v>0.217301980911731</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.1967321125121761</v>
+        <v>0.1982088926792122</v>
       </c>
     </row>
     <row r="37">
@@ -4451,46 +4440,46 @@
         <v>0.1964892583808794</v>
       </c>
       <c r="N37" t="n">
-        <v>0.2184204768528007</v>
+        <v>0.218165223325087</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1929749885906906</v>
+        <v>0.1929382111874333</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2258138864162601</v>
+        <v>0.2135027400525825</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.1980232914568188</v>
+        <v>0.2014324679448397</v>
       </c>
       <c r="R37" t="n">
-        <v>0.2153174454338602</v>
+        <v>0.2226398408582265</v>
       </c>
       <c r="S37" t="n">
-        <v>0.2000242603041565</v>
+        <v>0.1996862427510884</v>
       </c>
       <c r="T37" t="n">
-        <v>0.223187562274508</v>
+        <v>0.2151817343590304</v>
       </c>
       <c r="U37" t="n">
-        <v>0.2000698218587068</v>
+        <v>0.2000851453682307</v>
       </c>
       <c r="V37" t="n">
-        <v>0.2238729715709044</v>
+        <v>0.22263026394889</v>
       </c>
       <c r="W37" t="n">
-        <v>0.1959877245469688</v>
+        <v>0.1939850145282198</v>
       </c>
       <c r="X37" t="n">
-        <v>0.2340724559323785</v>
+        <v>0.2164493973928789</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.203957758625777</v>
+        <v>0.1933371572811243</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.2237081843243588</v>
+        <v>0.2168581460464038</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.1970611629069127</v>
+        <v>0.1962710647185108</v>
       </c>
     </row>
     <row r="38">
@@ -4534,46 +4523,46 @@
         <v>0.1955531393242383</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2160100648795401</v>
+        <v>0.2181939977636823</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2000924234805149</v>
+        <v>0.191504153382831</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2253632902491007</v>
+        <v>0.214197834160887</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.1958898991268869</v>
+        <v>0.1922808834215273</v>
       </c>
       <c r="R38" t="n">
-        <v>0.2153538292781873</v>
+        <v>0.217733521818776</v>
       </c>
       <c r="S38" t="n">
-        <v>0.1984866861259717</v>
+        <v>0.2009082378931516</v>
       </c>
       <c r="T38" t="n">
-        <v>0.2221823335117237</v>
+        <v>0.2121804440124653</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1953745029525163</v>
+        <v>0.204291677283258</v>
       </c>
       <c r="V38" t="n">
-        <v>0.223660836754413</v>
+        <v>0.2220215241286196</v>
       </c>
       <c r="W38" t="n">
-        <v>0.197874441619486</v>
+        <v>0.1931233100782511</v>
       </c>
       <c r="X38" t="n">
-        <v>0.233587107190108</v>
+        <v>0.2136636456890293</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.2063638135813785</v>
+        <v>0.1994682902539112</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.2174433542777253</v>
+        <v>0.216311346778015</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.2023247069476864</v>
+        <v>0.19884427107486</v>
       </c>
     </row>
     <row r="39">
@@ -4617,46 +4606,46 @@
         <v>0.1937758872078844</v>
       </c>
       <c r="N39" t="n">
-        <v>0.2156607953231197</v>
+        <v>0.2178754144240448</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1980200432806358</v>
+        <v>0.1937573114596594</v>
       </c>
       <c r="P39" t="n">
-        <v>0.2250597166005245</v>
+        <v>0.2130989223980337</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.1968412364335108</v>
+        <v>0.1928288543335692</v>
       </c>
       <c r="R39" t="n">
-        <v>0.2150721502536523</v>
+        <v>0.2171075797201065</v>
       </c>
       <c r="S39" t="n">
-        <v>0.1991932951129158</v>
+        <v>0.1990287721713858</v>
       </c>
       <c r="T39" t="n">
-        <v>0.2217485873213361</v>
+        <v>0.2121134009520131</v>
       </c>
       <c r="U39" t="n">
-        <v>0.1922839682273716</v>
+        <v>0.2023204551551933</v>
       </c>
       <c r="V39" t="n">
-        <v>0.2231366339385941</v>
+        <v>0.2207358276071258</v>
       </c>
       <c r="W39" t="n">
-        <v>0.197588503693671</v>
+        <v>0.1950089284828728</v>
       </c>
       <c r="X39" t="n">
-        <v>0.2320595805394687</v>
+        <v>0.2130328126228607</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.2040363036480679</v>
+        <v>0.1997454912704523</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.2159874993530372</v>
+        <v>0.2156533443422849</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.2009614632236778</v>
+        <v>0.2032906228363606</v>
       </c>
     </row>
     <row r="40">
@@ -4700,46 +4689,46 @@
         <v>0.1925480430343049</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2151542413856619</v>
+        <v>0.2170079912074403</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1956866740038151</v>
+        <v>0.194804262722884</v>
       </c>
       <c r="P40" t="n">
-        <v>0.2246434525509696</v>
+        <v>0.2131100861771294</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1962177819975627</v>
+        <v>0.1930963343155724</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2139553215878069</v>
+        <v>0.2169160103417687</v>
       </c>
       <c r="S40" t="n">
-        <v>0.1990946917414367</v>
+        <v>0.1957053446952822</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2216232252145602</v>
+        <v>0.2114868526739523</v>
       </c>
       <c r="U40" t="n">
-        <v>0.1952001549955027</v>
+        <v>0.2010395350652203</v>
       </c>
       <c r="V40" t="n">
-        <v>0.222774893618843</v>
+        <v>0.2197033223649872</v>
       </c>
       <c r="W40" t="n">
-        <v>0.1994736951191799</v>
+        <v>0.193213917657974</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2323609310633326</v>
+        <v>0.2130768777348471</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.2009974328201201</v>
+        <v>0.200054680208212</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.2159159850359948</v>
+        <v>0.2148326439552071</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.1979209501669385</v>
+        <v>0.2025232284928231</v>
       </c>
     </row>
     <row r="41">
@@ -4783,46 +4772,46 @@
         <v>0.1970703471021494</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2151161311810051</v>
+        <v>0.2177347287743483</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1927558680169732</v>
+        <v>0.1973812530012385</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2239784456112168</v>
+        <v>0.2128150790529557</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1976530781971471</v>
+        <v>0.1929520873456206</v>
       </c>
       <c r="R41" t="n">
-        <v>0.2132513911255504</v>
+        <v>0.216565146592007</v>
       </c>
       <c r="S41" t="n">
-        <v>0.1999509174172955</v>
+        <v>0.1961860203260243</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2167362523927115</v>
+        <v>0.2116646531715312</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1986211977794319</v>
+        <v>0.2027726400541701</v>
       </c>
       <c r="V41" t="n">
-        <v>0.2223356868225065</v>
+        <v>0.2193232829651741</v>
       </c>
       <c r="W41" t="n">
-        <v>0.1988392937268333</v>
+        <v>0.1934171842241829</v>
       </c>
       <c r="X41" t="n">
-        <v>0.2306174020790918</v>
+        <v>0.2128606401422361</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.2019142291045106</v>
+        <v>0.2018757116635013</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.2162530889488326</v>
+        <v>0.2148109652132781</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.2020875988944286</v>
+        <v>0.1952632967861963</v>
       </c>
     </row>
     <row r="42">
@@ -4866,46 +4855,46 @@
         <v>0.1937461459481133</v>
       </c>
       <c r="N42" t="n">
-        <v>0.2136128546115904</v>
+        <v>0.2167036013623838</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2006790212044157</v>
+        <v>0.1935093258930878</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2240088013701202</v>
+        <v>0.2129478133245071</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.1939532869812589</v>
+        <v>0.1936386880322786</v>
       </c>
       <c r="R42" t="n">
-        <v>0.2133699570867148</v>
+        <v>0.2145490242814845</v>
       </c>
       <c r="S42" t="n">
-        <v>0.1995031224113124</v>
+        <v>0.2009368507558902</v>
       </c>
       <c r="T42" t="n">
-        <v>0.215547752124065</v>
+        <v>0.2101664949970489</v>
       </c>
       <c r="U42" t="n">
-        <v>0.1973983557616434</v>
+        <v>0.2018289290202096</v>
       </c>
       <c r="V42" t="n">
-        <v>0.2172999605844336</v>
+        <v>0.2184717847680873</v>
       </c>
       <c r="W42" t="n">
-        <v>0.1973979134652161</v>
+        <v>0.1927322528292016</v>
       </c>
       <c r="X42" t="n">
-        <v>0.2292119706634524</v>
+        <v>0.2118226268313333</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.2011796347653416</v>
+        <v>0.1982481297713996</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.2128573557485111</v>
+        <v>0.2148612369783223</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.2034982399131029</v>
+        <v>0.1986136264591054</v>
       </c>
     </row>
     <row r="43">
@@ -4949,40 +4938,46 @@
         <v>0.1962910338673735</v>
       </c>
       <c r="N43" t="n">
-        <v>0.2132740359106832</v>
+        <v>0.2139941835044768</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2007634899692355</v>
+        <v>0.2051701705087728</v>
       </c>
       <c r="P43" t="n">
-        <v>0.2234437701192276</v>
+        <v>0.2140511516635576</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1952319593428532</v>
+        <v>0.1885013801687166</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.2141974867621729</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.2024294475038954</v>
       </c>
       <c r="T43" t="n">
-        <v>0.2153740570464841</v>
+        <v>0.2095989347320081</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1942998878614768</v>
+        <v>0.2018824847715007</v>
       </c>
       <c r="V43" t="n">
-        <v>0.2162398511836351</v>
+        <v>0.2179497480277003</v>
       </c>
       <c r="W43" t="n">
-        <v>0.1983242423613721</v>
+        <v>0.1959859342221027</v>
       </c>
       <c r="X43" t="n">
-        <v>0.2290329851040786</v>
+        <v>0.2113256620489492</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.2005253832913556</v>
+        <v>0.1986900614789803</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.212612537332341</v>
+        <v>0.2144660619164486</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.2040709887110328</v>
+        <v>0.1992054811129217</v>
       </c>
     </row>
     <row r="44">
@@ -5026,40 +5021,46 @@
         <v>0.1936505530416988</v>
       </c>
       <c r="N44" t="n">
-        <v>0.2130569187608694</v>
+        <v>0.2136456003943689</v>
       </c>
       <c r="O44" t="n">
-        <v>0.2016613923346133</v>
+        <v>0.2015747711297773</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2230368354357779</v>
+        <v>0.2127455935490218</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.1940919361371427</v>
+        <v>0.188145807060271</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.2138759240215598</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.1996369362135743</v>
       </c>
       <c r="T44" t="n">
-        <v>0.2145258181012613</v>
+        <v>0.2095602848990397</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1922705093648382</v>
+        <v>0.2026386483456188</v>
       </c>
       <c r="V44" t="n">
-        <v>0.2161141764795916</v>
+        <v>0.2174121184651701</v>
       </c>
       <c r="W44" t="n">
-        <v>0.1983035641201472</v>
+        <v>0.1928558815528964</v>
       </c>
       <c r="X44" t="n">
-        <v>0.2269295727341505</v>
+        <v>0.2111062114434855</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.1969697851966062</v>
+        <v>0.1994681519847966</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.2124206732712255</v>
+        <v>0.2140853071069607</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.2010315685419621</v>
+        <v>0.1994753534301472</v>
       </c>
     </row>
     <row r="45">
@@ -5103,40 +5104,40 @@
         <v>0.1962255422752035</v>
       </c>
       <c r="N45" t="n">
-        <v>0.2131072061236425</v>
+        <v>0.2131517744269068</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1990628170325939</v>
+        <v>0.1949503699860009</v>
       </c>
       <c r="P45" t="n">
-        <v>0.2227104168677749</v>
+        <v>0.2129308543868424</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1937157179735521</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.2126362203073896</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.1995581662675541</v>
+        <v>0.1881171001526075</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.2138489704917778</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.2009997485128041</v>
       </c>
       <c r="V45" t="n">
-        <v>0.2161627215417949</v>
+        <v>0.2170500693003809</v>
       </c>
       <c r="W45" t="n">
-        <v>0.1944640610160418</v>
+        <v>0.1966122534636907</v>
       </c>
       <c r="X45" t="n">
-        <v>0.2261553583243354</v>
+        <v>0.2110471181140458</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.1992970428290348</v>
+        <v>0.1992168834430089</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.2120357371697372</v>
+        <v>0.2133475936764528</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.2012685370403349</v>
+        <v>0.1998947972219397</v>
       </c>
     </row>
     <row r="46">
@@ -5180,40 +5181,40 @@
         <v>0.1944409227902744</v>
       </c>
       <c r="N46" t="n">
-        <v>0.2125403476717366</v>
+        <v>0.213042414366183</v>
       </c>
       <c r="O46" t="n">
-        <v>0.2002099981210058</v>
+        <v>0.1963413758863493</v>
       </c>
       <c r="P46" t="n">
-        <v>0.2226108980080313</v>
+        <v>0.2127940160460955</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1957875271808522</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0.211900991760964</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.1982531170654921</v>
+        <v>0.1882030765162939</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.2129495437795773</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.1987297587722356</v>
       </c>
       <c r="V46" t="n">
-        <v>0.2157614411909349</v>
+        <v>0.2159333773811679</v>
       </c>
       <c r="W46" t="n">
-        <v>0.1985137526014782</v>
+        <v>0.1943374052399824</v>
       </c>
       <c r="X46" t="n">
-        <v>0.2255205917249103</v>
+        <v>0.2113122880258713</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.1978174299948801</v>
+        <v>0.1922404779457073</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.2114066276968695</v>
+        <v>0.2109029792241506</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.2005753505670786</v>
+        <v>0.2066059468331272</v>
       </c>
     </row>
     <row r="47">
@@ -5251,40 +5252,40 @@
         <v>0.1911299674138886</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2123608128937377</v>
+        <v>0.2118269670600733</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2006770439577993</v>
+        <v>0.2060432162692624</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2219525858806061</v>
+        <v>0.2127738636572006</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.1937438957206618</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.2117391154785787</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.1983212466245497</v>
+        <v>0.1884035295914451</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.212507795030636</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.1988000450655818</v>
       </c>
       <c r="V47" t="n">
-        <v>0.2149663202556943</v>
+        <v>0.2132448002826884</v>
       </c>
       <c r="W47" t="n">
-        <v>0.1960106637595775</v>
+        <v>0.2030930798586877</v>
       </c>
       <c r="X47" t="n">
-        <v>0.2252188090288873</v>
+        <v>0.2104460878243808</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1965399723376602</v>
+        <v>0.1933723708517126</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.2105746982303594</v>
+        <v>0.2107985415149572</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.2003673197420311</v>
+        <v>0.2054099569151692</v>
       </c>
     </row>
     <row r="48">
@@ -5322,40 +5323,40 @@
         <v>0.1919718504881914</v>
       </c>
       <c r="N48" t="n">
-        <v>0.2114543618541981</v>
+        <v>0.2116050940230181</v>
       </c>
       <c r="O48" t="n">
-        <v>0.1999399777966765</v>
+        <v>0.2048305153462158</v>
       </c>
       <c r="P48" t="n">
-        <v>0.2220067317128058</v>
+        <v>0.2126476634986514</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1947370484766933</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0.2113664615976293</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0.198179584442823</v>
+        <v>0.188471797817833</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.2122414231046357</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.2000563296436322</v>
       </c>
       <c r="V48" t="n">
-        <v>0.2151781771378207</v>
+        <v>0.2127018996768377</v>
       </c>
       <c r="W48" t="n">
-        <v>0.1968251929154909</v>
+        <v>0.2038860200503942</v>
       </c>
       <c r="X48" t="n">
-        <v>0.2245896060543119</v>
+        <v>0.2106670670072771</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.1958452964528752</v>
+        <v>0.1936007622437113</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.210437487591489</v>
+        <v>0.2104392613761497</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.2002277205868959</v>
+        <v>0.2060474348548679</v>
       </c>
     </row>
     <row r="49">
@@ -5392,29 +5393,35 @@
       <c r="M49" t="n">
         <v>0.1909980549174253</v>
       </c>
+      <c r="N49" t="n">
+        <v>0.2113782329146158</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.2037067993003043</v>
+      </c>
       <c r="P49" t="n">
-        <v>0.2224318724441196</v>
+        <v>0.2125654366975727</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.194022755504504</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0.2106657435093845</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0.1988020863079786</v>
+        <v>0.1884772758658269</v>
       </c>
       <c r="V49" t="n">
-        <v>0.2147239789497569</v>
+        <v>0.2126202063542629</v>
       </c>
       <c r="W49" t="n">
-        <v>0.1960484792316226</v>
+        <v>0.2036407384375693</v>
       </c>
       <c r="X49" t="n">
-        <v>0.2237234459266313</v>
+        <v>0.2102876506969025</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.195676109500987</v>
+        <v>0.1939189086018133</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.210287569283146</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.2052920879652646</v>
       </c>
     </row>
     <row r="50">
@@ -5445,29 +5452,35 @@
       <c r="M50" t="n">
         <v>0.1915375374570397</v>
       </c>
+      <c r="N50" t="n">
+        <v>0.2114544759835463</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.2035660774336528</v>
+      </c>
       <c r="P50" t="n">
-        <v>0.2168282389078936</v>
+        <v>0.2133157958684505</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.1959416872286489</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0.209965764044607</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0.1981691423995859</v>
+        <v>0.187496309438419</v>
       </c>
       <c r="V50" t="n">
-        <v>0.2126749922744622</v>
+        <v>0.2127178110651795</v>
       </c>
       <c r="W50" t="n">
-        <v>0.2011546413780108</v>
+        <v>0.2023942100159675</v>
       </c>
       <c r="X50" t="n">
-        <v>0.2232351636760368</v>
+        <v>0.2101739379423401</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.1931804428795476</v>
+        <v>0.1940091963977953</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.2095135882042718</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.2009318988047001</v>
       </c>
     </row>
     <row r="51">
@@ -5498,29 +5511,35 @@
       <c r="M51" t="n">
         <v>0.1924781594827243</v>
       </c>
+      <c r="N51" t="n">
+        <v>0.2110058021623918</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.2003997654721531</v>
+      </c>
       <c r="P51" t="n">
-        <v>0.2159149650338083</v>
+        <v>0.2127728174894679</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1930901275830019</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.2096910929530551</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.1991528683429575</v>
+        <v>0.1874097002475007</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2122231221773223</v>
+        <v>0.2115194480404381</v>
       </c>
       <c r="W51" t="n">
-        <v>0.2020486960595098</v>
+        <v>0.2005248844612086</v>
       </c>
       <c r="X51" t="n">
-        <v>0.2231015404301488</v>
+        <v>0.2109830772027004</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.1949841763095239</v>
+        <v>0.1876245492104963</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.2090726138615965</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.2017982088987972</v>
       </c>
     </row>
     <row r="52">
@@ -5545,23 +5564,35 @@
       <c r="M52" t="n">
         <v>0.1950896040870821</v>
       </c>
+      <c r="N52" t="n">
+        <v>0.2106547932417617</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.201351118381659</v>
+      </c>
       <c r="P52" t="n">
-        <v>0.2152900334278291</v>
+        <v>0.2125283650099492</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.1931001681286285</v>
+        <v>0.187389389410879</v>
       </c>
       <c r="V52" t="n">
-        <v>0.2122957189721325</v>
+        <v>0.2107398814698758</v>
       </c>
       <c r="W52" t="n">
-        <v>0.1996814673077688</v>
+        <v>0.2007932994896417</v>
       </c>
       <c r="X52" t="n">
-        <v>0.2223708482251372</v>
+        <v>0.210043748756024</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.1972188808537664</v>
+        <v>0.1875610896551232</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.2086265130845968</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.2031220480432312</v>
       </c>
     </row>
     <row r="53">
@@ -5586,23 +5617,35 @@
       <c r="M53" t="n">
         <v>0.1911255475765063</v>
       </c>
+      <c r="N53" t="n">
+        <v>0.2104203209073152</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.2011215348479744</v>
+      </c>
       <c r="P53" t="n">
-        <v>0.2158773830352921</v>
+        <v>0.2124183278969558</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.1930087543148634</v>
+        <v>0.1873422176584326</v>
       </c>
       <c r="V53" t="n">
-        <v>0.2120335383864104</v>
+        <v>0.2106082101952869</v>
       </c>
       <c r="W53" t="n">
-        <v>0.2010973679254804</v>
+        <v>0.2017168871217475</v>
       </c>
       <c r="X53" t="n">
-        <v>0.2222815869368366</v>
+        <v>0.2100096660365989</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.1920384065260987</v>
+        <v>0.1877465439280165</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.2087611983191561</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.2039918341072641</v>
       </c>
     </row>
     <row r="54">
@@ -5628,22 +5671,28 @@
         <v>0.2027910379061507</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2156681954429662</v>
+        <v>0.2126576542230862</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.1928290893296454</v>
+        <v>0.1872854805874347</v>
       </c>
       <c r="V54" t="n">
-        <v>0.2110598634905374</v>
+        <v>0.2107007567624538</v>
       </c>
       <c r="W54" t="n">
-        <v>0.1992093661056691</v>
+        <v>0.2023520075152119</v>
       </c>
       <c r="X54" t="n">
-        <v>0.2219436433173962</v>
+        <v>0.2102913916157174</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.1925350226481977</v>
+        <v>0.1879882166816499</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.2088659319811123</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.1934341608829372</v>
       </c>
     </row>
     <row r="55">
@@ -5669,22 +5718,28 @@
         <v>0.200164891567041</v>
       </c>
       <c r="P55" t="n">
-        <v>0.2150669799124714</v>
+        <v>0.2126742456385419</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.1940567045542878</v>
+        <v>0.1873416758984764</v>
       </c>
       <c r="V55" t="n">
-        <v>0.2107020946766042</v>
+        <v>0.2106673459961148</v>
       </c>
       <c r="W55" t="n">
-        <v>0.1995146924382986</v>
+        <v>0.1926265504664651</v>
       </c>
       <c r="X55" t="n">
-        <v>0.2211150311025953</v>
+        <v>0.2095701129075663</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.1935085365362178</v>
+        <v>0.1880322083477821</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.2080558105602799</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.1940395357216406</v>
       </c>
     </row>
     <row r="56">
@@ -5710,22 +5765,28 @@
         <v>0.1987755391416707</v>
       </c>
       <c r="P56" t="n">
-        <v>0.2143743466585875</v>
+        <v>0.2121082589199597</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.1942716533295202</v>
+        <v>0.187221200865491</v>
       </c>
       <c r="V56" t="n">
-        <v>0.2104288336690053</v>
+        <v>0.2096494170760136</v>
       </c>
       <c r="W56" t="n">
-        <v>0.1996837437600586</v>
+        <v>0.1922423944253193</v>
       </c>
       <c r="X56" t="n">
-        <v>0.2216082802003881</v>
+        <v>0.2096654151042939</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.1929217529151652</v>
+        <v>0.1881179253331088</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.207713867299074</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.195109487070669</v>
       </c>
     </row>
     <row r="57">
@@ -5751,22 +5812,28 @@
         <v>0.1976935238834293</v>
       </c>
       <c r="P57" t="n">
-        <v>0.2143348421447349</v>
+        <v>0.2124398669212564</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.1922240301447193</v>
+        <v>0.1872800291058118</v>
       </c>
       <c r="V57" t="n">
-        <v>0.2101194649234353</v>
+        <v>0.2098683644440179</v>
       </c>
       <c r="W57" t="n">
-        <v>0.2000328226729607</v>
+        <v>0.1934786922368687</v>
       </c>
       <c r="X57" t="n">
-        <v>0.2209014227952469</v>
+        <v>0.2111921957693994</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.1982828469384456</v>
+        <v>0.1860138045664079</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.2078462664445878</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.1951478035913892</v>
       </c>
     </row>
     <row r="58">
@@ -5792,22 +5859,28 @@
         <v>0.2018357218517269</v>
       </c>
       <c r="P58" t="n">
-        <v>0.214464206879666</v>
+        <v>0.2123426255916268</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.1946178308468547</v>
+        <v>0.1872671352188535</v>
       </c>
       <c r="V58" t="n">
-        <v>0.2107423906453139</v>
+        <v>0.2092728537222571</v>
       </c>
       <c r="W58" t="n">
-        <v>0.1924228435453998</v>
+        <v>0.1940693692067417</v>
       </c>
       <c r="X58" t="n">
-        <v>0.2157547828810644</v>
+        <v>0.2097445450384509</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.195575243925449</v>
+        <v>0.1858689378766208</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.2078505757280187</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.1949863383153278</v>
       </c>
     </row>
     <row r="59">
@@ -5833,22 +5906,28 @@
         <v>0.2017888441676122</v>
       </c>
       <c r="P59" t="n">
-        <v>0.2143063801571665</v>
+        <v>0.2121032741274839</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1944150476686324</v>
+        <v>0.1873089704986874</v>
       </c>
       <c r="V59" t="n">
-        <v>0.2099371345536706</v>
+        <v>0.2092814065846961</v>
       </c>
       <c r="W59" t="n">
-        <v>0.1926433531386643</v>
+        <v>0.1941119327363436</v>
       </c>
       <c r="X59" t="n">
-        <v>0.2151119391287654</v>
+        <v>0.2099158685723674</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.1934867211372142</v>
+        <v>0.1858803111678118</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.2091631383157897</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.1868967553887671</v>
       </c>
     </row>
     <row r="60">
@@ -5874,22 +5953,28 @@
         <v>0.2017607672881903</v>
       </c>
       <c r="P60" t="n">
-        <v>0.2140861696809961</v>
+        <v>0.2121523086574267</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.1949132348171138</v>
+        <v>0.1873212623293691</v>
       </c>
       <c r="V60" t="n">
-        <v>0.2094037415082605</v>
+        <v>0.209019565881684</v>
       </c>
       <c r="W60" t="n">
-        <v>0.1937026293468999</v>
+        <v>0.1943740377831165</v>
       </c>
       <c r="X60" t="n">
-        <v>0.2145230442762744</v>
+        <v>0.2097319733228319</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.1922901799250825</v>
+        <v>0.1858972880891732</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.2080812236324938</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.1870774920435711</v>
       </c>
     </row>
     <row r="61">
@@ -5915,22 +6000,28 @@
         <v>0.2020559064449831</v>
       </c>
       <c r="P61" t="n">
-        <v>0.2136116422489593</v>
+        <v>0.2125141864011357</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1966798580172708</v>
+        <v>0.1872805818837877</v>
       </c>
       <c r="V61" t="n">
-        <v>0.2095888347926834</v>
+        <v>0.2106217661687781</v>
       </c>
       <c r="W61" t="n">
-        <v>0.1937651775536258</v>
+        <v>0.1874116271797378</v>
       </c>
       <c r="X61" t="n">
-        <v>0.2145008759088199</v>
+        <v>0.2095864318726846</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.1952193380205767</v>
+        <v>0.1858383228568983</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.207852575851004</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.1870467618957323</v>
       </c>
     </row>
     <row r="62">
@@ -5956,22 +6047,28 @@
         <v>0.1969135207093919</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2115909256895404</v>
+        <v>0.2121834318761614</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.2013413313911146</v>
+        <v>0.1873101206404517</v>
       </c>
       <c r="V62" t="n">
-        <v>0.2095363387483949</v>
+        <v>0.2094392768061173</v>
       </c>
       <c r="W62" t="n">
-        <v>0.193625779849734</v>
+        <v>0.1871178676280981</v>
       </c>
       <c r="X62" t="n">
-        <v>0.2124519095455935</v>
+        <v>0.2099382344802672</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.2003258973301226</v>
+        <v>0.1857863230464294</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.2079322075140316</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.1872594496852306</v>
       </c>
     </row>
     <row r="63">
@@ -5997,22 +6094,28 @@
         <v>0.1976139240428943</v>
       </c>
       <c r="P63" t="n">
-        <v>0.2113924418414427</v>
+        <v>0.2123920494836778</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.2006896876031174</v>
+        <v>0.1873307146723217</v>
       </c>
       <c r="V63" t="n">
-        <v>0.2106226737888083</v>
+        <v>0.2091868892504472</v>
       </c>
       <c r="W63" t="n">
-        <v>0.1875494750839398</v>
+        <v>0.1871462788587818</v>
       </c>
       <c r="X63" t="n">
-        <v>0.2120265005895298</v>
+        <v>0.2099385210351387</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.1985550170666746</v>
+        <v>0.1859085145887154</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.2075312083456203</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0.1874942889620761</v>
       </c>
     </row>
     <row r="64">
@@ -6038,22 +6141,28 @@
         <v>0.1970025462662379</v>
       </c>
       <c r="P64" t="n">
-        <v>0.211223714299931</v>
+        <v>0.2122018818150867</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.1986123979456137</v>
+        <v>0.1872921206189093</v>
       </c>
       <c r="V64" t="n">
-        <v>0.209498913035043</v>
+        <v>0.2093734454925457</v>
       </c>
       <c r="W64" t="n">
-        <v>0.1873416797041273</v>
+        <v>0.1872522293623015</v>
       </c>
       <c r="X64" t="n">
-        <v>0.2119000186366299</v>
+        <v>0.2097739779798329</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.1993564410014609</v>
+        <v>0.1857872655319598</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.2087269013801451</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.1852485182478404</v>
       </c>
     </row>
     <row r="65">
@@ -6073,22 +6182,28 @@
         <v>0.185371866735281</v>
       </c>
       <c r="P65" t="n">
-        <v>0.2111998278385967</v>
+        <v>0.2119845168603476</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.1990738651530103</v>
+        <v>0.1873299213964349</v>
       </c>
       <c r="V65" t="n">
-        <v>0.2090522068752792</v>
+        <v>0.2091612807582787</v>
       </c>
       <c r="W65" t="n">
-        <v>0.18745228927439</v>
+        <v>0.1871298501678443</v>
       </c>
       <c r="X65" t="n">
-        <v>0.2115540489061805</v>
+        <v>0.2099519044176237</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.1984795674793594</v>
+        <v>0.185836042406666</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.2077985494628487</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.1850672798239854</v>
       </c>
     </row>
     <row r="66">
@@ -6108,22 +6223,28 @@
         <v>0.1852815393760272</v>
       </c>
       <c r="P66" t="n">
-        <v>0.2103866172169358</v>
+        <v>0.2122262684659155</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.198548838844916</v>
+        <v>0.1873630122704939</v>
       </c>
       <c r="V66" t="n">
-        <v>0.2092340090004189</v>
+        <v>0.2092397889345576</v>
       </c>
       <c r="W66" t="n">
-        <v>0.1876471668212045</v>
+        <v>0.1873638379546844</v>
       </c>
       <c r="X66" t="n">
-        <v>0.2107233069413765</v>
+        <v>0.209422367236246</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.1989474770647455</v>
+        <v>0.1858838246374726</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.2078154157608563</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0.1849822846581393</v>
       </c>
     </row>
     <row r="67">
@@ -6143,22 +6264,28 @@
         <v>0.1854436707845064</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2099956011953802</v>
+        <v>0.2121592685580254</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.1992114379095094</v>
+        <v>0.1873748239247453</v>
       </c>
       <c r="V67" t="n">
-        <v>0.2090839324788429</v>
+        <v>0.2101345901639193</v>
       </c>
       <c r="W67" t="n">
-        <v>0.1877000038016972</v>
+        <v>0.18530305835615</v>
       </c>
       <c r="X67" t="n">
-        <v>0.2105451921224286</v>
+        <v>0.2099680135696203</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.199933047600102</v>
+        <v>0.1856515349401233</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.2078131541363464</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.1851110114530877</v>
       </c>
     </row>
     <row r="68">
@@ -6178,22 +6305,28 @@
         <v>0.1854788004327422</v>
       </c>
       <c r="P68" t="n">
-        <v>0.2098675941363408</v>
+        <v>0.2116796054323165</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.1991801875268894</v>
+        <v>0.1873700605728341</v>
       </c>
       <c r="V68" t="n">
-        <v>0.2091160039725321</v>
+        <v>0.2093355469020807</v>
       </c>
       <c r="W68" t="n">
-        <v>0.1878190789736222</v>
+        <v>0.1851097733465429</v>
       </c>
       <c r="X68" t="n">
-        <v>0.2099917417522982</v>
+        <v>0.2097063155282935</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.1994482890447352</v>
+        <v>0.1856509755453086</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.2071133522693961</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.1849951167161848</v>
       </c>
     </row>
     <row r="69">
@@ -6213,16 +6346,28 @@
         <v>0.1854679969588556</v>
       </c>
       <c r="P69" t="n">
-        <v>0.2100457081240255</v>
+        <v>0.2117567981770339</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.1990076875578159</v>
+        <v>0.187387285438382</v>
       </c>
       <c r="V69" t="n">
-        <v>0.2100826694576208</v>
+        <v>0.2091164751755736</v>
       </c>
       <c r="W69" t="n">
-        <v>0.1857952015081245</v>
+        <v>0.1851223239772745</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0.2096850002523173</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0.1856716656239448</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.2078364029418954</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.1849845739968339</v>
       </c>
     </row>
     <row r="70">
@@ -6242,16 +6387,28 @@
         <v>0.1853389907255195</v>
       </c>
       <c r="P70" t="n">
-        <v>0.2106624136232455</v>
+        <v>0.2117338599675635</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.1901865728136342</v>
+        <v>0.1874000459725758</v>
       </c>
       <c r="V70" t="n">
-        <v>0.209171340723853</v>
+        <v>0.2090996837797613</v>
       </c>
       <c r="W70" t="n">
-        <v>0.1856631301946146</v>
+        <v>0.1850174671320247</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0.2093778057985993</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0.1856400918628797</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.2078058837166379</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.1850367760822429</v>
       </c>
     </row>
     <row r="71">
@@ -6271,16 +6428,28 @@
         <v>0.1843169022391684</v>
       </c>
       <c r="P71" t="n">
-        <v>0.2096569592264012</v>
+        <v>0.212072434153962</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.1901009990726074</v>
+        <v>0.1874111906477524</v>
       </c>
       <c r="V71" t="n">
-        <v>0.209257701365662</v>
+        <v>0.2089813534239661</v>
       </c>
       <c r="W71" t="n">
-        <v>0.1856322882134462</v>
+        <v>0.1850871742704455</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.2098624790318249</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0.1856558305743755</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.2079173750782863</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.1848067901827659</v>
       </c>
     </row>
     <row r="72">
@@ -6299,17 +6468,23 @@
       <c r="E72" t="n">
         <v>0.184305092794835</v>
       </c>
-      <c r="P72" t="n">
-        <v>0.2096425695498743</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0.1908036222902395</v>
-      </c>
       <c r="V72" t="n">
-        <v>0.2089148311113769</v>
+        <v>0.2090364674121634</v>
       </c>
       <c r="W72" t="n">
-        <v>0.1856309859245694</v>
+        <v>0.1851143980289713</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0.2096946402337433</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.1857110312042072</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.2075071549735779</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.184770547431852</v>
       </c>
     </row>
     <row r="73">
@@ -6328,17 +6503,23 @@
       <c r="E73" t="n">
         <v>0.1842904835408453</v>
       </c>
-      <c r="P73" t="n">
-        <v>0.2097268743625234</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0.1912344081157988</v>
-      </c>
       <c r="V73" t="n">
-        <v>0.2090736859408784</v>
+        <v>0.2089723301628097</v>
       </c>
       <c r="W73" t="n">
-        <v>0.1856385711953618</v>
+        <v>0.1849663592344049</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.2097514050989604</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0.1857375279241148</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.2077973875879071</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.1847803622702329</v>
       </c>
     </row>
     <row r="74">
@@ -6357,17 +6538,23 @@
       <c r="E74" t="n">
         <v>0.1842422842066764</v>
       </c>
-      <c r="P74" t="n">
-        <v>0.2091779672417574</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0.191246028692506</v>
-      </c>
       <c r="V74" t="n">
-        <v>0.2092360212152039</v>
+        <v>0.2089986642014451</v>
       </c>
       <c r="W74" t="n">
-        <v>0.1856592584455899</v>
+        <v>0.1849864239980953</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.2092130266414755</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0.1857426227063216</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.2074082482352176</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.1847477183162087</v>
       </c>
     </row>
     <row r="75">
@@ -6386,17 +6573,23 @@
       <c r="E75" t="n">
         <v>0.1841987050576092</v>
       </c>
-      <c r="P75" t="n">
-        <v>0.2092974145650432</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0.1908128423378078</v>
-      </c>
       <c r="V75" t="n">
-        <v>0.2090146676868139</v>
+        <v>0.2088013177406628</v>
       </c>
       <c r="W75" t="n">
-        <v>0.1856483033167999</v>
+        <v>0.1850322580943673</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2094458681377313</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.185733129052253</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2071336622865609</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1847455667788148</v>
       </c>
     </row>
     <row r="76">
@@ -6415,17 +6608,23 @@
       <c r="E76" t="n">
         <v>0.1841571551025809</v>
       </c>
-      <c r="P76" t="n">
-        <v>0.2106148222892368</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0.1857107168849908</v>
-      </c>
       <c r="V76" t="n">
-        <v>0.2094209740738854</v>
+        <v>0.2087201192428566</v>
       </c>
       <c r="W76" t="n">
-        <v>0.1854772027208827</v>
+        <v>0.1850856403434198</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0.2095467843084542</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0.1857651464342612</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.2076223901134323</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0.1847482198226525</v>
       </c>
     </row>
     <row r="77">
@@ -6444,17 +6643,23 @@
       <c r="E77" t="n">
         <v>0.1841314502493787</v>
       </c>
-      <c r="P77" t="n">
-        <v>0.2097781703053119</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0.1856232985412165</v>
-      </c>
       <c r="V77" t="n">
-        <v>0.209417017261413</v>
+        <v>0.2086016076755487</v>
       </c>
       <c r="W77" t="n">
-        <v>0.1854526194053571</v>
+        <v>0.1850636182037198</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0.2095388883747899</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0.1857841944118218</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.2072293239045303</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0.184763867511358</v>
       </c>
     </row>
     <row r="78">
@@ -6473,17 +6678,23 @@
       <c r="E78" t="n">
         <v>0.1841648611037752</v>
       </c>
-      <c r="P78" t="n">
-        <v>0.2096636514410315</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0.1855461997150778</v>
-      </c>
       <c r="V78" t="n">
-        <v>0.208816858262501</v>
+        <v>0.2090862037629382</v>
       </c>
       <c r="W78" t="n">
-        <v>0.1854291712873843</v>
+        <v>0.1849015226260471</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0.2095867637660324</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0.1857873974970681</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.2074978386613825</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0.184741204047722</v>
       </c>
     </row>
     <row r="79">
@@ -6502,17 +6713,23 @@
       <c r="E79" t="n">
         <v>0.1842078102080981</v>
       </c>
-      <c r="P79" t="n">
-        <v>0.2097621445336248</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0.1854907487001046</v>
-      </c>
       <c r="V79" t="n">
-        <v>0.208763582093164</v>
+        <v>0.2087649851806523</v>
       </c>
       <c r="W79" t="n">
-        <v>0.1854054731573732</v>
+        <v>0.1848920014283644</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0.2092199753161735</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0.1857940536882091</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.2076550641651304</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0.1847857786457303</v>
       </c>
     </row>
     <row r="80">
@@ -6531,17 +6748,23 @@
       <c r="E80" t="n">
         <v>0.1841941178261155</v>
       </c>
-      <c r="P80" t="n">
-        <v>0.2094468364938478</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0.1855463804591028</v>
-      </c>
       <c r="V80" t="n">
-        <v>0.2088237611907881</v>
+        <v>0.2088529645188227</v>
       </c>
       <c r="W80" t="n">
-        <v>0.1853864060482369</v>
+        <v>0.1849072567303486</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0.2096826042979956</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0.1858098463590138</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.2071982155946538</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.1848012915595746</v>
       </c>
     </row>
     <row r="81">
@@ -6560,17 +6783,23 @@
       <c r="E81" t="n">
         <v>0.1842372331995006</v>
       </c>
-      <c r="P81" t="n">
-        <v>0.2093528361321419</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0.185705206892202</v>
-      </c>
       <c r="V81" t="n">
-        <v>0.2091545062255084</v>
+        <v>0.2089668828955551</v>
       </c>
       <c r="W81" t="n">
-        <v>0.1854145007870965</v>
+        <v>0.1849344352472614</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0.2089430154532133</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0.1858187227542921</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.2073797927899979</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0.1848253725808349</v>
       </c>
     </row>
     <row r="82">
@@ -6589,17 +6818,23 @@
       <c r="E82" t="n">
         <v>0.1842518777432973</v>
       </c>
-      <c r="P82" t="n">
-        <v>0.2095499998612776</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0.1857269167590123</v>
-      </c>
       <c r="V82" t="n">
-        <v>0.208922414355411</v>
+        <v>0.2083232915182867</v>
       </c>
       <c r="W82" t="n">
-        <v>0.1854122320307743</v>
+        <v>0.1849024461608133</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0.2093915101256191</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0.1858204228685844</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0.2069642790054425</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0.1848116133804038</v>
       </c>
     </row>
     <row r="83">
@@ -6618,17 +6853,23 @@
       <c r="E83" t="n">
         <v>0.1842816716335565</v>
       </c>
-      <c r="P83" t="n">
-        <v>0.2094244489692583</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0.1857839393758076</v>
-      </c>
       <c r="V83" t="n">
-        <v>0.2090741144223831</v>
+        <v>0.2089507353438203</v>
       </c>
       <c r="W83" t="n">
-        <v>0.1854151421842181</v>
+        <v>0.1850211646218421</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0.2091216821885429</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0.1858249742290915</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0.2072310740135856</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0.1848379976872372</v>
       </c>
     </row>
     <row r="84">
@@ -6647,17 +6888,23 @@
       <c r="E84" t="n">
         <v>0.1842897193182047</v>
       </c>
-      <c r="P84" t="n">
-        <v>0.2102883770207543</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0.184823545876988</v>
-      </c>
       <c r="V84" t="n">
-        <v>0.2089749038188664</v>
+        <v>0.2085916182865227</v>
       </c>
       <c r="W84" t="n">
-        <v>0.1854408573106689</v>
+        <v>0.1850720704726886</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0.2094571901646958</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0.1858273653789941</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0.207147447003652</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0.1848509560765351</v>
       </c>
     </row>
     <row r="85">
@@ -6676,17 +6923,23 @@
       <c r="E85" t="n">
         <v>0.1842833056526462</v>
       </c>
-      <c r="P85" t="n">
-        <v>0.2092916162238141</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0.1847492107914873</v>
-      </c>
       <c r="V85" t="n">
-        <v>0.2089046220187375</v>
+        <v>0.2084264493016295</v>
       </c>
       <c r="W85" t="n">
-        <v>0.1854702783432805</v>
+        <v>0.1850798252226644</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0.2090405653584902</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0.1858326635238799</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0.20688634304222</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0.1848487324814652</v>
       </c>
     </row>
     <row r="86">
@@ -6705,17 +6958,17 @@
       <c r="E86" t="n">
         <v>0.1843454415891291</v>
       </c>
-      <c r="P86" t="n">
-        <v>0.2093539210036397</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0.184690866425622</v>
-      </c>
       <c r="V86" t="n">
-        <v>0.2090284007308958</v>
+        <v>0.208453421265441</v>
       </c>
       <c r="W86" t="n">
-        <v>0.1854817935442107</v>
+        <v>0.185095363989679</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0.2072286550340451</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0.1848708024443642</v>
       </c>
     </row>
     <row r="87">
@@ -6734,17 +6987,17 @@
       <c r="E87" t="n">
         <v>0.184386604192892</v>
       </c>
-      <c r="P87" t="n">
-        <v>0.2095141323583493</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0.1846338279103324</v>
-      </c>
       <c r="V87" t="n">
-        <v>0.2089309477408932</v>
+        <v>0.2084354701113295</v>
       </c>
       <c r="W87" t="n">
-        <v>0.185493677241788</v>
+        <v>0.1851350634239717</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0.2070722423555437</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0.1848785426591068</v>
       </c>
     </row>
     <row r="88">
@@ -6763,17 +7016,17 @@
       <c r="E88" t="n">
         <v>0.1844179252885822</v>
       </c>
-      <c r="P88" t="n">
-        <v>0.209227435706445</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0.1845954359940989</v>
-      </c>
       <c r="V88" t="n">
-        <v>0.2088067506185987</v>
+        <v>0.2084525169820086</v>
       </c>
       <c r="W88" t="n">
-        <v>0.1854814907840133</v>
+        <v>0.1851636414805022</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0.206722772776434</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0.1848858817364269</v>
       </c>
     </row>
     <row r="89">
@@ -6792,17 +7045,17 @@
       <c r="E89" t="n">
         <v>0.1844267435988931</v>
       </c>
-      <c r="P89" t="n">
-        <v>0.209668006170695</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0.1846541073201985</v>
-      </c>
       <c r="V89" t="n">
-        <v>0.2091963702451037</v>
+        <v>0.2083529009953264</v>
       </c>
       <c r="W89" t="n">
-        <v>0.1855097071200219</v>
+        <v>0.1851785272727211</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0.2071302328643597</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0.1848918763541822</v>
       </c>
     </row>
     <row r="90">
@@ -6821,17 +7074,17 @@
       <c r="E90" t="n">
         <v>0.184453542944107</v>
       </c>
-      <c r="P90" t="n">
-        <v>0.209398746425055</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0.184686237125326</v>
-      </c>
       <c r="V90" t="n">
-        <v>0.2086859857894419</v>
+        <v>0.2081976290061023</v>
       </c>
       <c r="W90" t="n">
-        <v>0.1855209465705444</v>
+        <v>0.1851930585553516</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0.207237831759459</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0.1848986267280092</v>
       </c>
     </row>
     <row r="91">
@@ -6850,17 +7103,17 @@
       <c r="E91" t="n">
         <v>0.1844721712209342</v>
       </c>
-      <c r="P91" t="n">
-        <v>0.2093800488005061</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0.1847510951153578</v>
-      </c>
       <c r="V91" t="n">
-        <v>0.2086228994837354</v>
+        <v>0.2083789559720038</v>
       </c>
       <c r="W91" t="n">
-        <v>0.1855307127562895</v>
+        <v>0.1852082689859559</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0.2068486871959811</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0.1849021132036653</v>
       </c>
     </row>
     <row r="92">
@@ -6879,17 +7132,17 @@
       <c r="E92" t="n">
         <v>0.1844846845930227</v>
       </c>
-      <c r="P92" t="n">
-        <v>0.209261063882727</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0.1847005039467857</v>
-      </c>
       <c r="V92" t="n">
-        <v>0.2088430609038361</v>
+        <v>0.2084841702541352</v>
       </c>
       <c r="W92" t="n">
-        <v>0.1855409996360196</v>
+        <v>0.1852186376484361</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0.2070891864613191</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0.1849063706206867</v>
       </c>
     </row>
     <row r="93">
@@ -6902,17 +7155,17 @@
       <c r="C93" t="n">
         <v>0.184700543576068</v>
       </c>
-      <c r="P93" t="n">
-        <v>0.2091678955230462</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0.1847720741680343</v>
-      </c>
       <c r="V93" t="n">
-        <v>0.2090686886255776</v>
+        <v>0.208460566822501</v>
       </c>
       <c r="W93" t="n">
-        <v>0.1855541116289668</v>
+        <v>0.1852305549008912</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0.2070461577920567</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0.1849102097346759</v>
       </c>
     </row>
     <row r="94">
@@ -6925,17 +7178,11 @@
       <c r="C94" t="n">
         <v>0.1847084877633695</v>
       </c>
-      <c r="P94" t="n">
-        <v>0.2089447037178315</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0.1848338167376828</v>
-      </c>
       <c r="V94" t="n">
-        <v>0.2087117617080096</v>
+        <v>0.2084381661323969</v>
       </c>
       <c r="W94" t="n">
-        <v>0.1855612924503297</v>
+        <v>0.1852349405964759</v>
       </c>
     </row>
     <row r="95">
@@ -6948,18 +7195,6 @@
       <c r="C95" t="n">
         <v>0.184717319432204</v>
       </c>
-      <c r="P95" t="n">
-        <v>0.2094232127385999</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0.1848444017453926</v>
-      </c>
-      <c r="V95" t="n">
-        <v>0.208911784716751</v>
-      </c>
-      <c r="W95" t="n">
-        <v>0.185570533512209</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6971,12 +7206,6 @@
       <c r="C96" t="n">
         <v>0.1847226309456586</v>
       </c>
-      <c r="P96" t="n">
-        <v>0.2095010855219766</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0.1848676120704514</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6987,56 +7216,6 @@
       </c>
       <c r="C97" t="n">
         <v>0.1847259120209191</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0.2094008208806665</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0.1849629937574979</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0.2091141021502597</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0.185018196275805</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0.2090380438834367</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0.1850535555546085</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0.2093995515341786</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0.1850778154787738</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0.2093922670599658</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0.1851137461031691</v>
       </c>
     </row>
   </sheetData>
